--- a/human_resources_forms/023_employee_performance_appraisal_feedback_form--human_resources_forms.xlsx
+++ b/human_resources_forms/023_employee_performance_appraisal_feedback_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'operations'}</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'Operations'}</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'leadership_and_initiative'}</t>
+          <t>leadership_and_initiative</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'Leadership and Initiative'}</t>
+          <t>Leadership and Initiative</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_50,_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 50, 'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_60,_'label':_'collaboration_and_teamwork'}</t>
+          <t>collaboration_and_teamwork</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 60, 'label': 'Collaboration and Teamwork'}</t>
+          <t>Collaboration and Teamwork</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_70,_'label':_'problem_solving_and_analysis'}</t>
+          <t>problem_solving_and_analysis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 70, 'label': 'Problem Solving and Analysis'}</t>
+          <t>Problem Solving and Analysis</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_80,_'label':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 80, 'label': 'Time Management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_90,_'label':_'adaptability_and_flexibility'}</t>
+          <t>adaptability_and_flexibility</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 90, 'label': 'Adaptability and Flexibility'}</t>
+          <t>Adaptability and Flexibility</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_100,_'label':_'continuous_improvement'}</t>
+          <t>continuous_improvement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 100, 'label': 'Continuous Improvement'}</t>
+          <t>Continuous Improvement</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_110,_'label':_'below_expectations'}</t>
+          <t>below_expectations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 110, 'label': 'Below Expectations'}</t>
+          <t>Below Expectations</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_120,_'label':_'meets_expectations'}</t>
+          <t>meets_expectations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 120, 'label': 'Meets Expectations'}</t>
+          <t>Meets Expectations</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_130,_'label':_'exceeds_expectations'}</t>
+          <t>exceeds_expectations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 130, 'label': 'Exceeds Expectations'}</t>
+          <t>Exceeds Expectations</t>
         </is>
       </c>
     </row>
